--- a/corr_matrix/residual_exam1B_3PL.xlsx
+++ b/corr_matrix/residual_exam1B_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>1B01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1289176606237709</v>
+        <v>-0.1290141631028372</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0315445364657081</v>
+        <v>-0.03147937223055526</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.06625919104540538</v>
+        <v>-0.06621808342001387</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1466567860439346</v>
+        <v>-0.1466324171230788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01217414044948618</v>
+        <v>0.01227530092753091</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1017348022577115</v>
+        <v>-0.1018202859825532</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1095126917441907</v>
+        <v>0.1093369025276739</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.08947661580504263</v>
+        <v>-0.08961734475431182</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.09450243329665785</v>
+        <v>-0.09432474017991341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007151745549091028</v>
+        <v>0.007074865201391621</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02840946124708432</v>
+        <v>-0.02841755002070763</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4148941747200691</v>
+        <v>0.4147600138902669</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1249790073266902</v>
+        <v>-0.1249850769574591</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1566557241667705</v>
+        <v>-0.1566944283516389</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1243520572954554</v>
+        <v>0.1243279439287195</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1289176606237709</v>
+        <v>-0.1290141631028372</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09436963056083107</v>
+        <v>-0.0943557455566597</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1128332336242718</v>
+        <v>-0.1127967024368499</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0276771039439555</v>
+        <v>-0.02783517631049135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03309666046155144</v>
+        <v>0.03318595885043742</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02996594716617013</v>
+        <v>-0.02991835188294051</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0208324603192258</v>
+        <v>-0.02088784665198121</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1211040592133026</v>
+        <v>-0.1211019325442261</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.143111759582947</v>
+        <v>-0.1429479879511208</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1347646551581022</v>
+        <v>-0.1347888912703413</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01797989974908958</v>
+        <v>-0.01801853520995014</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1312876872959407</v>
+        <v>-0.1313717014252365</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04122988553080884</v>
+        <v>0.04125890206167924</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02537953814999639</v>
+        <v>0.02534055272521337</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1671084196996354</v>
+        <v>-0.1672089360690643</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0315445364657081</v>
+        <v>-0.03147937223055526</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09436963056083107</v>
+        <v>-0.0943557455566597</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06786494873716856</v>
+        <v>-0.0677856854642532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006259442531067158</v>
+        <v>0.006171082575806163</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1301509485450084</v>
+        <v>-0.1300509049995942</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.002700054712173507</v>
+        <v>-0.002637913325898273</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2832867645454302</v>
+        <v>-0.2833038471428787</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02812441165599639</v>
+        <v>0.02816021684194454</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02950682390531688</v>
+        <v>0.02966947177955456</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01242206369210447</v>
+        <v>-0.01256481643222897</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3740909442482385</v>
+        <v>-0.3740915965407147</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07626950812262782</v>
+        <v>0.07633588873730959</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.009660526677477814</v>
+        <v>-0.009582679526026204</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2490359155684358</v>
+        <v>-0.2490463715261869</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07077535480814572</v>
+        <v>0.07071629412112981</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.06625919104540538</v>
+        <v>-0.06621808342001387</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1128332336242718</v>
+        <v>-0.1127967024368499</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06786494873716856</v>
+        <v>-0.0677856854642532</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06546247262958828</v>
+        <v>0.06530783716857011</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.09714450567680646</v>
+        <v>-0.097050299845267</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01024095330690929</v>
+        <v>-0.01014919938208012</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06360612251100078</v>
+        <v>0.0636261720375418</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.09462322628669466</v>
+        <v>-0.09455827094408088</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02943490292482093</v>
+        <v>0.02961314078442598</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2816255977800211</v>
+        <v>-0.281724641314699</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1613877917133709</v>
+        <v>-0.1613761448774468</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06910652287110475</v>
+        <v>-0.06906964845003438</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1255090045204986</v>
+        <v>-0.1254087404476102</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1176620642786222</v>
+        <v>-0.1176646209818994</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.06280318476609699</v>
+        <v>-0.06289482313507876</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1466567860439346</v>
+        <v>-0.1466324171230788</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0276771039439555</v>
+        <v>-0.02783517631049135</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006259442531067158</v>
+        <v>0.006171082575806163</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06546247262958828</v>
+        <v>0.06530783716857011</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3161500581996943</v>
+        <v>-0.3163082257666897</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1867248280558609</v>
+        <v>-0.1868099324746816</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1005659730613749</v>
+        <v>-0.10064066499656</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0873959919123609</v>
+        <v>-0.08745034210345115</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1596382961116075</v>
+        <v>-0.1597300981748721</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1011809672581547</v>
+        <v>-0.1009378930876355</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0529580364899692</v>
+        <v>-0.05308757248568099</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1196643530450525</v>
+        <v>0.1196942999498037</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.08104978679650135</v>
+        <v>-0.08116307675881365</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.003838513350349718</v>
+        <v>-0.004025547066454531</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.03574939362823158</v>
+        <v>-0.03556648994982185</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01217414044948618</v>
+        <v>0.01227530092753091</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03309666046155144</v>
+        <v>0.03318595885043742</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1301509485450084</v>
+        <v>-0.1300509049995942</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09714450567680646</v>
+        <v>-0.097050299845267</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3161500581996943</v>
+        <v>-0.3163082257666897</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0102738963703192</v>
+        <v>0.01042966352263174</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0840832812597636</v>
+        <v>-0.08399709003529607</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1295907781278468</v>
+        <v>-0.1294387697776989</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001789483758026816</v>
+        <v>0.002006867069508426</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1088616575112961</v>
+        <v>-0.1089711525761592</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01501003428026058</v>
+        <v>0.01507304960456383</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0879376516846741</v>
+        <v>-0.08785844055682074</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01083014174222148</v>
+        <v>0.01094586098525317</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.09644887456549493</v>
+        <v>-0.096432633171952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1864342562138406</v>
+        <v>-0.1866890822448934</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1017348022577115</v>
+        <v>-0.1018202859825532</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.02996594716617013</v>
+        <v>-0.02991835188294051</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002700054712173507</v>
+        <v>-0.002637913325898273</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01024095330690929</v>
+        <v>-0.01014919938208012</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1867248280558609</v>
+        <v>-0.1868099324746816</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0102738963703192</v>
+        <v>0.01042966352263174</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06531937703992227</v>
+        <v>-0.06533343216971982</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1547389488736679</v>
+        <v>0.1547756744450335</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1157320362903347</v>
+        <v>-0.115541954740486</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0204652681605322</v>
+        <v>-0.02066493585197256</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07292928376539864</v>
+        <v>-0.07289041877106366</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3004958194684136</v>
+        <v>-0.3005529803046721</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06629578171809931</v>
+        <v>-0.06622782762096721</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1291814415000128</v>
+        <v>-0.1291350643610484</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2314917469488957</v>
+        <v>-0.2315838434669071</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1095126917441907</v>
+        <v>0.1093369025276739</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0208324603192258</v>
+        <v>-0.02088784665198121</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2832867645454302</v>
+        <v>-0.2833038471428787</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06360612251100078</v>
+        <v>0.0636261720375418</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1005659730613749</v>
+        <v>-0.10064066499656</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0840832812597636</v>
+        <v>-0.08399709003529607</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.06531937703992227</v>
+        <v>-0.06533343216971982</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0399596088168909</v>
+        <v>-0.04002086336987363</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1541291108461533</v>
+        <v>-0.154007766056849</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01743424340983513</v>
+        <v>0.01742185321578013</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007202162858755553</v>
+        <v>0.007145722705820515</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01659675931628176</v>
+        <v>-0.01678716586109624</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01673740366451092</v>
+        <v>-0.01676321289043794</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1859505467688399</v>
+        <v>-0.1860178916133216</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03708648255145713</v>
+        <v>0.03704942798793649</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08947661580504263</v>
+        <v>-0.08961734475431182</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1211040592133026</v>
+        <v>-0.1211019325442261</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02812441165599639</v>
+        <v>0.02816021684194454</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09462322628669466</v>
+        <v>-0.09455827094408088</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0873959919123609</v>
+        <v>-0.08745034210345115</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1295907781278468</v>
+        <v>-0.1294387697776989</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1547389488736679</v>
+        <v>0.1547756744450335</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0399596088168909</v>
+        <v>-0.04002086336987363</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1045039279743563</v>
+        <v>-0.1043418520600953</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1071348071476603</v>
+        <v>-0.107266468763784</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.100062119767699</v>
+        <v>-0.1000692182243761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1944387366616098</v>
+        <v>-0.1945507270573565</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04530750242291008</v>
+        <v>-0.04527418516454341</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1532785713073797</v>
+        <v>-0.153278913806524</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.08836112118813165</v>
+        <v>0.08832390236271069</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.09450243329665785</v>
+        <v>-0.09432474017991341</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.143111759582947</v>
+        <v>-0.1429479879511208</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02950682390531688</v>
+        <v>0.02966947177955456</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02943490292482093</v>
+        <v>0.02961314078442598</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1596382961116075</v>
+        <v>-0.1597300981748721</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001789483758026816</v>
+        <v>0.002006867069508426</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1157320362903347</v>
+        <v>-0.115541954740486</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1541291108461533</v>
+        <v>-0.154007766056849</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1045039279743563</v>
+        <v>-0.1043418520600953</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06015194433940017</v>
+        <v>0.05978069981679985</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2316359086337689</v>
+        <v>-0.2314722295238308</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004168635549951571</v>
+        <v>0.004343655841091679</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07775114882652819</v>
+        <v>0.07791145748317682</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1719328004856153</v>
+        <v>-0.1717698225728091</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1605294481146413</v>
+        <v>-0.1606545964912502</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.007151745549091028</v>
+        <v>0.007074865201391621</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1347646551581022</v>
+        <v>-0.1347888912703413</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01242206369210447</v>
+        <v>-0.01256481643222897</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2816255977800211</v>
+        <v>-0.281724641314699</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1011809672581547</v>
+        <v>-0.1009378930876355</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1088616575112961</v>
+        <v>-0.1089711525761592</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0204652681605322</v>
+        <v>-0.02066493585197256</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01743424340983513</v>
+        <v>0.01742185321578013</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1071348071476603</v>
+        <v>-0.107266468763784</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06015194433940017</v>
+        <v>0.05978069981679985</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1583162377079512</v>
+        <v>-0.1583094457177467</v>
       </c>
       <c r="N12" t="n">
-        <v>0.005151662404843218</v>
+        <v>0.005106948717682183</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1533670151766739</v>
+        <v>-0.1534700962139449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.006208279160529692</v>
+        <v>-0.006157245221914428</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1047217322887192</v>
+        <v>-0.104463207091977</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02840946124708432</v>
+        <v>-0.02841755002070763</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.01797989974908958</v>
+        <v>-0.01801853520995014</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3740909442482385</v>
+        <v>-0.3740915965407147</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1613877917133709</v>
+        <v>-0.1613761448774468</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0529580364899692</v>
+        <v>-0.05308757248568099</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01501003428026058</v>
+        <v>0.01507304960456383</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.07292928376539864</v>
+        <v>-0.07289041877106366</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007202162858755553</v>
+        <v>0.007145722705820515</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.100062119767699</v>
+        <v>-0.1000692182243761</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2316359086337689</v>
+        <v>-0.2314722295238308</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1583162377079512</v>
+        <v>-0.1583094457177467</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1444507901896072</v>
+        <v>-0.1444852707961287</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1887136561769196</v>
+        <v>-0.1886856315042161</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6003262814931376</v>
+        <v>0.60029803478396</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.08918782905486081</v>
+        <v>-0.08925603180503452</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4148941747200691</v>
+        <v>0.4147600138902669</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1312876872959407</v>
+        <v>-0.1313717014252365</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07626950812262782</v>
+        <v>0.07633588873730959</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.06910652287110475</v>
+        <v>-0.06906964845003438</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1196643530450525</v>
+        <v>0.1196942999498037</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0879376516846741</v>
+        <v>-0.08785844055682074</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3004958194684136</v>
+        <v>-0.3005529803046721</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01659675931628176</v>
+        <v>-0.01678716586109624</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1944387366616098</v>
+        <v>-0.1945507270573565</v>
       </c>
       <c r="K14" t="n">
-        <v>0.004168635549951571</v>
+        <v>0.004343655841091679</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005151662404843218</v>
+        <v>0.005106948717682183</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1444507901896072</v>
+        <v>-0.1444852707961287</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1140037101248734</v>
+        <v>0.1140347687009838</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1629084178251153</v>
+        <v>-0.1629408077542032</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02103174851081191</v>
+        <v>0.02099860105959151</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1249790073266902</v>
+        <v>-0.1249850769574591</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04122988553080884</v>
+        <v>0.04125890206167924</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.009660526677477814</v>
+        <v>-0.009582679526026204</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1255090045204986</v>
+        <v>-0.1254087404476102</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08104978679650135</v>
+        <v>-0.08116307675881365</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01083014174222148</v>
+        <v>0.01094586098525317</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06629578171809931</v>
+        <v>-0.06622782762096721</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.01673740366451092</v>
+        <v>-0.01676321289043794</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04530750242291008</v>
+        <v>-0.04527418516454341</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07775114882652819</v>
+        <v>0.07791145748317682</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1533670151766739</v>
+        <v>-0.1534700962139449</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1887136561769196</v>
+        <v>-0.1886856315042161</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1140037101248734</v>
+        <v>0.1140347687009838</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1715639942915876</v>
+        <v>-0.1715314130416813</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1275356896579422</v>
+        <v>-0.1276407457225663</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1566557241667705</v>
+        <v>-0.1566944283516389</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02537953814999639</v>
+        <v>0.02534055272521337</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2490359155684358</v>
+        <v>-0.2490463715261869</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1176620642786222</v>
+        <v>-0.1176646209818994</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.003838513350349718</v>
+        <v>-0.004025547066454531</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.09644887456549493</v>
+        <v>-0.096432633171952</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1291814415000128</v>
+        <v>-0.1291350643610484</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1859505467688399</v>
+        <v>-0.1860178916133216</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1532785713073797</v>
+        <v>-0.153278913806524</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1719328004856153</v>
+        <v>-0.1717698225728091</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.006208279160529692</v>
+        <v>-0.006157245221914428</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6003262814931376</v>
+        <v>0.60029803478396</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1629084178251153</v>
+        <v>-0.1629408077542032</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1715639942915876</v>
+        <v>-0.1715314130416813</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1414839812728669</v>
+        <v>-0.1416005633144774</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1243520572954554</v>
+        <v>0.1243279439287195</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1671084196996354</v>
+        <v>-0.1672089360690643</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07077535480814572</v>
+        <v>0.07071629412112981</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06280318476609699</v>
+        <v>-0.06289482313507876</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.03574939362823158</v>
+        <v>-0.03556648994982185</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1864342562138406</v>
+        <v>-0.1866890822448934</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2314917469488957</v>
+        <v>-0.2315838434669071</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03708648255145713</v>
+        <v>0.03704942798793649</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08836112118813165</v>
+        <v>0.08832390236271069</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1605294481146413</v>
+        <v>-0.1606545964912502</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1047217322887192</v>
+        <v>-0.104463207091977</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.08918782905486081</v>
+        <v>-0.08925603180503452</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02103174851081191</v>
+        <v>0.02099860105959151</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1275356896579422</v>
+        <v>-0.1276407457225663</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1414839812728669</v>
+        <v>-0.1416005633144774</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
